--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126434631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82806611</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100204689</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101763</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118290998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984676</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68330549</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1713,6 +1758,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328600</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1829,6 +1879,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101457</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101554</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2039,6 +2099,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68330544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2139,6 +2204,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68330550</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118290918</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118290979</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2487,6 +2567,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101560</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2593,6 +2678,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101622</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2699,6 +2789,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101707</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2805,6 +2900,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101755</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2911,6 +3011,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101801</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3017,6 +3122,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101843</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3123,6 +3233,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101985</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3234,8 +3349,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340636</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125984676</v>
+        <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>58815</v>
+        <v>56859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,54 +1425,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208250</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormkärret, Sura sn, Vstm</t>
+          <t>Ormkärret, Surahammar, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557917</v>
+        <v>557878</v>
       </c>
       <c r="R8" t="n">
-        <v>6617684</v>
+        <v>6617676</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,22 +1492,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz). Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid upprepade tillfällen, med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,87 +1521,76 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125984676</t>
+          <t>https://artportalen.se/Sighting/135867093</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68330549</v>
+        <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>99017</v>
+        <v>56838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219795</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Degran, Lisjö, Sura sn, Vstm</t>
+          <t>Ormkärret, Surahammar, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557848</v>
+        <v>557878</v>
       </c>
       <c r="R9" t="n">
-        <v>6617812</v>
+        <v>6617676</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,12 +1614,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-05-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-05-27</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz). Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid upprepade tillfällen under båda inventeringsnätterna, med hög klassificeringssäkerhet. Hög aktivitet noterades under kvällen den 11 augusti mellan kl. 21:49 och 23:09. Ett flertal sekvenser klassificerades som feeding buzz, vilket indikerar aktivt födosök vid lokalen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,68 +1649,78 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68330549</t>
+          <t>https://artportalen.se/Sighting/135866979</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68328600</v>
+        <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>99153</v>
+        <v>56861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>206002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Degran, Lisjö, Sura sn, Vstm</t>
+          <t>Ormkärret, Surahammar, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557850</v>
+        <v>557878</v>
       </c>
       <c r="R10" t="n">
-        <v>6617743</v>
+        <v>6617676</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1729,12 +1744,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-05-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-05-27</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz). Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid upprepade tillfällen under båda inventeringsnätterna, med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,59 +1779,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68328600</t>
+          <t>https://artportalen.se/Sighting/135867016</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101457</v>
+        <v>125984676</v>
       </c>
       <c r="B11" t="n">
-        <v>102241</v>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1809,10 +1848,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557743</v>
+        <v>557917</v>
       </c>
       <c r="R11" t="n">
-        <v>6617730</v>
+        <v>6617684</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1839,22 +1878,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,49 +1914,49 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Sören Larsson, Greta Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101457</t>
+          <t>https://artportalen.se/Sighting/125984676</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101554</v>
+        <v>68330549</v>
       </c>
       <c r="B12" t="n">
-        <v>102241</v>
+        <v>99017</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>219795</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1927,21 +1966,20 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ormkärret, Sura sn, Vstm</t>
+          <t>Degran, Lisjö, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557753</v>
+        <v>557848</v>
       </c>
       <c r="R12" t="n">
-        <v>6617735</v>
+        <v>6617812</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1968,12 +2006,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2017-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2017-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,7 +2020,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1994,22 +2031,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101554</t>
+          <t>https://artportalen.se/Sighting/68330549</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68330544</v>
+        <v>68328600</v>
       </c>
       <c r="B13" t="n">
-        <v>97977</v>
+        <v>99153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,19 +2054,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221944</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -2040,10 +2081,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557849</v>
+        <v>557850</v>
       </c>
       <c r="R13" t="n">
-        <v>6617778</v>
+        <v>6617743</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2101,54 +2142,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68330544</t>
+          <t>https://artportalen.se/Sighting/68328600</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68330550</v>
+        <v>120101457</v>
       </c>
       <c r="B14" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Degran, Lisjö, Sura sn, Vstm</t>
+          <t>Ormkärret, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557848</v>
+        <v>557743</v>
       </c>
       <c r="R14" t="n">
-        <v>6617812</v>
+        <v>6617730</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2175,12 +2221,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-05-27</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-05-27</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,6 +2245,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2200,48 +2257,56 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68330550</t>
+          <t>https://artportalen.se/Sighting/120101457</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118290918</v>
+        <v>120101554</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2255,10 +2320,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557850</v>
+        <v>557753</v>
       </c>
       <c r="R15" t="n">
-        <v>6617782</v>
+        <v>6617735</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2285,27 +2350,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,22 +2376,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118290918</t>
+          <t>https://artportalen.se/Sighting/120101554</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118290979</v>
+        <v>68330544</v>
       </c>
       <c r="B16" t="n">
-        <v>101326</v>
+        <v>97977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,42 +2399,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ormkärret, Sura sn, Vstm</t>
+          <t>Degran, Lisjö, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557856</v>
+        <v>557849</v>
       </c>
       <c r="R16" t="n">
-        <v>6617791</v>
+        <v>6617778</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2411,27 +2452,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-05-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
+          <t>2017-05-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,7 +2466,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2452,19 +2477,19 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118290979</t>
+          <t>https://artportalen.se/Sighting/68330544</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120101560</v>
+        <v>68330550</v>
       </c>
       <c r="B17" t="n">
         <v>101326</v>
@@ -2494,23 +2519,18 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ormkärret, Sura sn, Vstm</t>
+          <t>Degran, Lisjö, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557753</v>
+        <v>557848</v>
       </c>
       <c r="R17" t="n">
-        <v>6617735</v>
+        <v>6617812</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2537,12 +2557,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2017-05-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2017-05-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2551,7 +2571,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2563,19 +2582,19 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101560</t>
+          <t>https://artportalen.se/Sighting/68330550</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120101622</v>
+        <v>118290918</v>
       </c>
       <c r="B18" t="n">
         <v>101326</v>
@@ -2618,10 +2637,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557743</v>
+        <v>557850</v>
       </c>
       <c r="R18" t="n">
-        <v>6617730</v>
+        <v>6617782</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2648,12 +2667,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,19 +2708,19 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101622</t>
+          <t>https://artportalen.se/Sighting/118290918</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120101707</v>
+        <v>118290979</v>
       </c>
       <c r="B19" t="n">
         <v>101326</v>
@@ -2729,10 +2763,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557754</v>
+        <v>557856</v>
       </c>
       <c r="R19" t="n">
-        <v>6617723</v>
+        <v>6617791</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2759,12 +2793,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,19 +2834,19 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101707</t>
+          <t>https://artportalen.se/Sighting/118290979</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120101755</v>
+        <v>120101560</v>
       </c>
       <c r="B20" t="n">
         <v>101326</v>
@@ -2840,10 +2889,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557750</v>
+        <v>557753</v>
       </c>
       <c r="R20" t="n">
-        <v>6617708</v>
+        <v>6617735</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2902,13 +2951,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101755</t>
+          <t>https://artportalen.se/Sighting/120101560</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120101801</v>
+        <v>120101622</v>
       </c>
       <c r="B21" t="n">
         <v>101326</v>
@@ -2951,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557730</v>
+        <v>557743</v>
       </c>
       <c r="R21" t="n">
-        <v>6617705</v>
+        <v>6617730</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3013,13 +3062,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101801</t>
+          <t>https://artportalen.se/Sighting/120101622</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120101843</v>
+        <v>120101707</v>
       </c>
       <c r="B22" t="n">
         <v>101326</v>
@@ -3062,10 +3111,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557744</v>
+        <v>557754</v>
       </c>
       <c r="R22" t="n">
-        <v>6617695</v>
+        <v>6617723</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3124,13 +3173,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101843</t>
+          <t>https://artportalen.se/Sighting/120101707</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120101985</v>
+        <v>120101755</v>
       </c>
       <c r="B23" t="n">
         <v>101326</v>
@@ -3173,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557747</v>
+        <v>557750</v>
       </c>
       <c r="R23" t="n">
-        <v>6617712</v>
+        <v>6617708</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3229,22 +3278,22 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Greta Larsson, Sören Larsson</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101985</t>
+          <t>https://artportalen.se/Sighting/120101755</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130340636</v>
+        <v>120101801</v>
       </c>
       <c r="B24" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,17 +3329,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Degran, Vstm</t>
+          <t>Ormkärret, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557801</v>
+        <v>557730</v>
       </c>
       <c r="R24" t="n">
-        <v>6617851</v>
+        <v>6617705</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3314,12 +3363,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,24 +3381,357 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101801</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120101843</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ormkärret, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>557744</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6617695</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101843</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120101985</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ormkärret, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>557747</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6617712</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Greta Larsson, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101985</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130340636</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Degran, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>557801</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6617851</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130340636</t>
         </is>
@@ -3380,6 +3762,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>56859</v>
+        <v>56861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>56861</v>
+        <v>56863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>56861</v>
+        <v>56862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>56863</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>56862</v>
+        <v>56866</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>56868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>56866</v>
+        <v>56867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>56868</v>
+        <v>56869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>56867</v>
+        <v>56872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>56869</v>
+        <v>56874</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31059-2026 artfynd.xlsx
+++ b/artfynd/A 31059-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>135867093</v>
       </c>
       <c r="B8" t="n">
-        <v>56872</v>
+        <v>56885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135866979</v>
       </c>
       <c r="B9" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135867016</v>
       </c>
       <c r="B10" t="n">
-        <v>56874</v>
+        <v>56887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
